--- a/Models/Верблюды/Датасет по верблюдам wide.xlsx
+++ b/Models/Верблюды/Датасет по верблюдам wide.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U121"/>
+  <dimension ref="A1:U128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7877,6 +7877,475 @@
         <v>764.4399999999999</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" t="n">
+        <v>129.3</v>
+      </c>
+      <c r="D122" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E122" t="n">
+        <v>322.1</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="K122" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>450.07</v>
+      </c>
+      <c r="O122" t="n">
+        <v>164</v>
+      </c>
+      <c r="P122" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="n">
+        <v>69.2</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="D123" t="n">
+        <v>19</v>
+      </c>
+      <c r="E123" t="n">
+        <v>286.54</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="K123" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
+        <v>376.72</v>
+      </c>
+      <c r="O123" t="n">
+        <v>580.5</v>
+      </c>
+      <c r="P123" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="n">
+        <v>60.13</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" t="n">
+        <v>411.5</v>
+      </c>
+      <c r="D124" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E124" t="n">
+        <v>447.4</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="K124" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="L124" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="n">
+        <v>335.32</v>
+      </c>
+      <c r="O124" t="n">
+        <v>109.58</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="n">
+        <v>93.09999999999999</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" t="n">
+        <v>128.1</v>
+      </c>
+      <c r="D125" t="n">
+        <v>12</v>
+      </c>
+      <c r="E125" t="n">
+        <v>266.8</v>
+      </c>
+      <c r="F125" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L125" t="n">
+        <v>2</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="O125" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="n">
+        <v>85.80000000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" t="n">
+        <v>235.7</v>
+      </c>
+      <c r="D126" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="E126" t="n">
+        <v>496.55</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="K126" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L126" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="O126" t="n">
+        <v>174.45</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="n">
+        <v>96.61000000000001</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="D127" t="n">
+        <v>41.59999999999999</v>
+      </c>
+      <c r="E127" t="n">
+        <v>688</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="K127" t="n">
+        <v>59.92</v>
+      </c>
+      <c r="L127" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
+        <v>56.94</v>
+      </c>
+      <c r="O127" t="n">
+        <v>317.85</v>
+      </c>
+      <c r="P127" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" t="n">
+        <v>25.17</v>
+      </c>
+      <c r="D128" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E128" t="n">
+        <v>212.7</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="O128" t="n">
+        <v>163.8</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="n">
+        <v>44.09999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Models/Верблюды/Датасет по верблюдам wide.xlsx
+++ b/Models/Верблюды/Датасет по верблюдам wide.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U128"/>
+  <dimension ref="A1:S128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,75 +461,65 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ГАЛМАТЫ</t>
+          <t>ГАСТАНА</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>ГАСТАНА</t>
+          <t>ЖАМБЫЛСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>ГШЫМКЕНТ</t>
+          <t>ЗАПАДНО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>ЖАМБЫЛСКАЯ ОБЛАСТЬ</t>
+          <t>КАРАГАНДИНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>ЗАПАДНО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>КОСТАНАЙСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>КАРАГАНДИНСКАЯ ОБЛАСТЬ</t>
+          <t>КЫЗЫЛОРДИНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>КОСТАНАЙСКАЯ ОБЛАСТЬ</t>
+          <t>МАНГИСТАУСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>КЫЗЫЛОРДИНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>МАНГИСТАУСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ АБАЙ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
@@ -541,9 +531,7 @@
           <t>2015-01</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>101.98</v>
       </c>
@@ -556,41 +544,29 @@
       <c r="F2" t="n">
         <v>0.3</v>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>68.46000000000001</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5.81</v>
+      </c>
       <c r="J2" t="n">
-        <v>68.46000000000001</v>
-      </c>
-      <c r="K2" t="n">
-        <v>5.81</v>
-      </c>
+        <v>1.56</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>1.56</v>
+        <v>277.14</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>277.14</v>
-      </c>
-      <c r="O2" t="n">
         <v>175.14</v>
       </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -598,9 +574,7 @@
           <t>2015-02</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>67.47</v>
       </c>
@@ -610,44 +584,30 @@
       <c r="E3" t="n">
         <v>167.7</v>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>36.1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5.34</v>
+      </c>
       <c r="J3" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>5.34</v>
-      </c>
+        <v>3.14</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>3.14</v>
+        <v>191.49</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>191.49</v>
-      </c>
-      <c r="O3" t="n">
         <v>128.3</v>
       </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -667,44 +627,32 @@
       <c r="E4" t="n">
         <v>306.6</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>64.28999999999999</v>
+      </c>
+      <c r="I4" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="J4" t="n">
-        <v>64.28999999999999</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>8.800000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="L4" t="n">
-        <v>9.449999999999999</v>
+        <v>178.37</v>
       </c>
       <c r="M4" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="N4" t="n">
-        <v>178.37</v>
-      </c>
-      <c r="O4" t="n">
         <v>87.04000000000001</v>
       </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -712,9 +660,7 @@
           <t>2015-04</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>115.59</v>
       </c>
@@ -727,41 +673,31 @@
       <c r="F5" t="n">
         <v>1.14</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>22.05</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.15</v>
+      </c>
       <c r="J5" t="n">
-        <v>22.05</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.15</v>
-      </c>
+        <v>6.87</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>6.87</v>
+        <v>110.29</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>110.29</v>
-      </c>
-      <c r="O5" t="n">
         <v>45.56999999999999</v>
       </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>0.96</v>
+      </c>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -769,56 +705,40 @@
           <t>2015-05</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>218.72</v>
       </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
         <v>342.57</v>
       </c>
       <c r="F6" t="n">
         <v>6.12</v>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>6.7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>15.82</v>
+      </c>
       <c r="J6" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K6" t="n">
-        <v>15.82</v>
-      </c>
+        <v>3.45</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O6" t="n">
         <v>210</v>
       </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -826,9 +746,7 @@
           <t>2015-06</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>14.15</v>
       </c>
@@ -841,41 +759,29 @@
       <c r="F7" t="n">
         <v>4.7</v>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>16.95</v>
+      </c>
+      <c r="I7" t="n">
+        <v>56.78</v>
+      </c>
       <c r="J7" t="n">
-        <v>16.95</v>
-      </c>
-      <c r="K7" t="n">
-        <v>56.78</v>
-      </c>
+        <v>6.73</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>6.73</v>
+        <v>0.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O7" t="n">
         <v>309.09</v>
       </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -898,41 +804,27 @@
       <c r="F8" t="n">
         <v>4.2</v>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
         <v>17.38</v>
       </c>
-      <c r="K8" t="n">
+      <c r="I8" t="n">
         <v>3.03</v>
       </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O8" t="n">
         <v>43.61</v>
       </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -955,41 +847,29 @@
       <c r="F9" t="n">
         <v>1.8</v>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>9.609999999999999</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
       <c r="J9" t="n">
-        <v>9.609999999999999</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2</v>
-      </c>
+        <v>0.43</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>0.43</v>
+        <v>4.8</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O9" t="n">
         <v>202.49</v>
       </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -997,9 +877,7 @@
           <t>2015-09</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>39.16</v>
       </c>
@@ -1012,41 +890,33 @@
       <c r="F10" t="n">
         <v>1.8</v>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>49.69</v>
+      </c>
+      <c r="I10" t="n">
+        <v>20.5</v>
+      </c>
       <c r="J10" t="n">
-        <v>49.69</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>20.5</v>
+        <v>1.12</v>
       </c>
       <c r="L10" t="n">
-        <v>9.300000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="M10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O10" t="n">
         <v>247.21</v>
       </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
+      <c r="Q10" t="n">
+        <v>1.6</v>
+      </c>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1054,9 +924,7 @@
           <t>2015-10</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>46.16</v>
       </c>
@@ -1066,44 +934,30 @@
       <c r="E11" t="n">
         <v>193.97</v>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
+        <v>27.48</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.54</v>
+      </c>
       <c r="J11" t="n">
-        <v>27.48</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4.54</v>
-      </c>
+        <v>44.11</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>44.11</v>
+        <v>1.55</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="O11" t="n">
         <v>41.52</v>
       </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1126,41 +980,29 @@
       <c r="F12" t="n">
         <v>6.82</v>
       </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>45.96</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.72</v>
+      </c>
       <c r="J12" t="n">
-        <v>45.96</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.72</v>
-      </c>
+        <v>10.97</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>10.97</v>
+        <v>205.9</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>205.9</v>
-      </c>
-      <c r="O12" t="n">
         <v>207.2</v>
       </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1168,9 +1010,7 @@
           <t>2015-12</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>463.35</v>
       </c>
@@ -1183,41 +1023,29 @@
       <c r="F13" t="n">
         <v>18.78</v>
       </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>16.35</v>
+      </c>
+      <c r="I13" t="n">
+        <v>11.38</v>
+      </c>
       <c r="J13" t="n">
-        <v>16.35</v>
-      </c>
-      <c r="K13" t="n">
-        <v>11.38</v>
-      </c>
+        <v>23.81</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>23.81</v>
+        <v>544.9400000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>544.9400000000001</v>
-      </c>
-      <c r="O13" t="n">
         <v>473.27</v>
       </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1225,9 +1053,7 @@
           <t>2016-01</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>109.04</v>
       </c>
@@ -1240,41 +1066,29 @@
       <c r="F14" t="n">
         <v>0.74</v>
       </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>64.53</v>
+      </c>
+      <c r="I14" t="n">
+        <v>20.88</v>
+      </c>
       <c r="J14" t="n">
-        <v>64.53</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20.88</v>
-      </c>
+        <v>1.19</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>1.19</v>
+        <v>298.8</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>298.8</v>
-      </c>
-      <c r="O14" t="n">
         <v>166.92</v>
       </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1294,44 +1108,30 @@
       <c r="E15" t="n">
         <v>190.6</v>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
+        <v>38.07</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7.4</v>
+      </c>
       <c r="J15" t="n">
-        <v>38.07</v>
-      </c>
-      <c r="K15" t="n">
-        <v>7.4</v>
-      </c>
+        <v>1.96</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>1.96</v>
+        <v>230.49</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>230.49</v>
-      </c>
-      <c r="O15" t="n">
         <v>253.13</v>
       </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1354,41 +1154,29 @@
       <c r="F16" t="n">
         <v>1.8</v>
       </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
+        <v>52.33</v>
+      </c>
+      <c r="I16" t="n">
+        <v>7.87</v>
+      </c>
       <c r="J16" t="n">
-        <v>52.33</v>
-      </c>
-      <c r="K16" t="n">
-        <v>7.87</v>
-      </c>
+        <v>22.75</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>22.75</v>
+        <v>182.42</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>182.42</v>
-      </c>
-      <c r="O16" t="n">
         <v>9</v>
       </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1396,9 +1184,7 @@
           <t>2016-04</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>114.35</v>
       </c>
@@ -1411,41 +1197,31 @@
       <c r="F17" t="n">
         <v>2.38</v>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
+        <v>22.13</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.05</v>
+      </c>
       <c r="J17" t="n">
-        <v>22.13</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2.05</v>
-      </c>
+        <v>6.91</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>6.91</v>
+        <v>7.8</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O17" t="n">
         <v>119.24</v>
       </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
+      <c r="Q17" t="n">
+        <v>1.86</v>
+      </c>
       <c r="R17" t="inlineStr"/>
-      <c r="S17" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1453,9 +1229,7 @@
           <t>2016-05</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>221.89</v>
       </c>
@@ -1468,41 +1242,29 @@
       <c r="F18" t="n">
         <v>1.22</v>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
+        <v>8.029999999999999</v>
+      </c>
+      <c r="I18" t="n">
+        <v>11.78</v>
+      </c>
       <c r="J18" t="n">
-        <v>8.029999999999999</v>
-      </c>
-      <c r="K18" t="n">
-        <v>11.78</v>
-      </c>
+        <v>5.38</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>5.38</v>
+        <v>3.3</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O18" t="n">
         <v>155.02</v>
       </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1525,41 +1287,29 @@
       <c r="F19" t="n">
         <v>2.4</v>
       </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>18.76</v>
+      </c>
+      <c r="I19" t="n">
+        <v>61.92</v>
+      </c>
       <c r="J19" t="n">
-        <v>18.76</v>
-      </c>
-      <c r="K19" t="n">
-        <v>61.92</v>
-      </c>
-      <c r="L19" t="n">
         <v>4.12</v>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
         <v>155.53</v>
       </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+      <c r="Q19" t="n">
+        <v>1.2</v>
+      </c>
       <c r="R19" t="inlineStr"/>
-      <c r="S19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1567,9 +1317,7 @@
           <t>2016-07</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>18.79</v>
       </c>
@@ -1582,41 +1330,27 @@
       <c r="F20" t="n">
         <v>3.2</v>
       </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
         <v>18.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="I20" t="n">
         <v>0.4</v>
       </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O20" t="n">
         <v>144.16</v>
       </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1624,56 +1358,40 @@
           <t>2016-08</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>3.5</v>
       </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
         <v>118.2</v>
       </c>
       <c r="F21" t="n">
         <v>2.45</v>
       </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
+        <v>9.690000000000001</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9</v>
+      </c>
       <c r="J21" t="n">
-        <v>9.690000000000001</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L21" t="n">
         <v>0.85</v>
       </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
         <v>186.91</v>
       </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+      <c r="Q21" t="n">
+        <v>0.37</v>
+      </c>
       <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1696,41 +1414,31 @@
       <c r="F22" t="n">
         <v>0.9</v>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
+        <v>52.7</v>
+      </c>
+      <c r="I22" t="n">
+        <v>13.3</v>
+      </c>
       <c r="J22" t="n">
-        <v>52.7</v>
+        <v>4.98</v>
       </c>
       <c r="K22" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="L22" t="n">
-        <v>4.98</v>
-      </c>
+        <v>2.71</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
         <v>640.91</v>
       </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+      <c r="Q22" t="n">
+        <v>0.12</v>
+      </c>
       <c r="R22" t="inlineStr"/>
-      <c r="S22" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1738,9 +1446,7 @@
           <t>2016-10</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>46.64</v>
       </c>
@@ -1753,41 +1459,29 @@
       <c r="F23" t="n">
         <v>2.2</v>
       </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
+        <v>27.51</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.7</v>
+      </c>
       <c r="J23" t="n">
-        <v>27.51</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1.7</v>
-      </c>
+        <v>18.71</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>18.71</v>
+        <v>13.09</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>13.09</v>
-      </c>
-      <c r="O23" t="n">
         <v>335.16</v>
       </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1810,41 +1504,29 @@
       <c r="F24" t="n">
         <v>0.74</v>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>44.08</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4.6</v>
+      </c>
       <c r="J24" t="n">
-        <v>44.08</v>
-      </c>
-      <c r="K24" t="n">
-        <v>4.6</v>
-      </c>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>8.699999999999999</v>
+        <v>229.3</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>229.3</v>
-      </c>
-      <c r="O24" t="n">
         <v>359.96</v>
       </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1867,41 +1549,29 @@
       <c r="F25" t="n">
         <v>12.46</v>
       </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
+        <v>12.96</v>
+      </c>
+      <c r="I25" t="n">
+        <v>16.5</v>
+      </c>
       <c r="J25" t="n">
-        <v>12.96</v>
-      </c>
-      <c r="K25" t="n">
-        <v>16.5</v>
-      </c>
+        <v>44.63</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>44.63</v>
+        <v>371.25</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>371.25</v>
-      </c>
-      <c r="O25" t="n">
         <v>522.38</v>
       </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1909,9 +1579,7 @@
           <t>2017-01</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>110.32</v>
       </c>
@@ -1924,41 +1592,29 @@
       <c r="F26" t="n">
         <v>0.74</v>
       </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
+        <v>55.49</v>
+      </c>
+      <c r="I26" t="n">
+        <v>18.04</v>
+      </c>
       <c r="J26" t="n">
-        <v>55.49</v>
-      </c>
-      <c r="K26" t="n">
-        <v>18.04</v>
-      </c>
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>0.8300000000000001</v>
+        <v>335.49</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>335.49</v>
-      </c>
-      <c r="O26" t="n">
         <v>209.47</v>
       </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1966,9 +1622,7 @@
           <t>2017-02</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>68.17</v>
       </c>
@@ -1982,40 +1636,32 @@
         <v>2.7</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="H27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
+        <v>40.95</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5.449999999999999</v>
+      </c>
       <c r="J27" t="n">
-        <v>40.95</v>
-      </c>
-      <c r="K27" t="n">
-        <v>5.449999999999999</v>
-      </c>
+        <v>0.46</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>0.46</v>
+        <v>236.83</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>236.83</v>
-      </c>
-      <c r="O27" t="n">
         <v>283.8200000000001</v>
       </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+      <c r="Q27" t="n">
+        <v>0.75</v>
+      </c>
       <c r="R27" t="inlineStr"/>
-      <c r="S27" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2023,14 +1669,12 @@
           <t>2017-03</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>380.15</v>
       </c>
       <c r="D28" t="n">
-        <v>41.59999999999999</v>
+        <v>41.6</v>
       </c>
       <c r="E28" t="n">
         <v>323.54</v>
@@ -2038,41 +1682,29 @@
       <c r="F28" t="n">
         <v>1.8</v>
       </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="inlineStr"/>
+        <v>39.59</v>
+      </c>
+      <c r="I28" t="n">
+        <v>6.1</v>
+      </c>
       <c r="J28" t="n">
-        <v>39.59</v>
-      </c>
-      <c r="K28" t="n">
-        <v>6.1</v>
-      </c>
+        <v>19.04</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
-        <v>19.04</v>
+        <v>242.01</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>242.01</v>
-      </c>
-      <c r="O28" t="n">
         <v>18.12</v>
       </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2080,9 +1712,7 @@
           <t>2017-04</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>127.12</v>
       </c>
@@ -2092,44 +1722,30 @@
       <c r="E29" t="n">
         <v>182.34</v>
       </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
+        <v>23.12</v>
+      </c>
+      <c r="I29" t="n">
+        <v>6.9</v>
+      </c>
       <c r="J29" t="n">
-        <v>23.12</v>
-      </c>
-      <c r="K29" t="n">
-        <v>6.9</v>
-      </c>
+        <v>4.6</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>4.6</v>
+        <v>6.36</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="O29" t="n">
         <v>150.98</v>
       </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2137,9 +1753,7 @@
           <t>2017-05</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>217.61</v>
       </c>
@@ -2149,44 +1763,30 @@
       <c r="E30" t="n">
         <v>349.1</v>
       </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="inlineStr"/>
+        <v>8.5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>14.75</v>
+      </c>
       <c r="J30" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K30" t="n">
-        <v>14.75</v>
-      </c>
+        <v>3.45</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>3.45</v>
+        <v>1.4</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O30" t="n">
         <v>149.85</v>
       </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2209,41 +1809,27 @@
       <c r="F31" t="n">
         <v>3</v>
       </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="inlineStr"/>
+        <v>17.27</v>
+      </c>
+      <c r="I31" t="n">
+        <v>51.90000000000001</v>
+      </c>
       <c r="J31" t="n">
-        <v>17.27</v>
-      </c>
-      <c r="K31" t="n">
-        <v>51.90000000000001</v>
-      </c>
-      <c r="L31" t="n">
         <v>14.7</v>
       </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
         <v>160.8</v>
       </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2251,9 +1837,7 @@
           <t>2017-07</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>21.26</v>
       </c>
@@ -2263,44 +1847,28 @@
       <c r="E32" t="n">
         <v>57.57</v>
       </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="inlineStr"/>
+        <v>16.15</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.8</v>
+      </c>
       <c r="J32" t="n">
-        <v>16.15</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L32" t="n">
         <v>1.59</v>
       </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
         <v>154.66</v>
       </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2320,44 +1888,26 @@
       <c r="E33" t="n">
         <v>88.40000000000001</v>
       </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>9.440000000000001</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>9.440000000000001</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
         <v>0.89</v>
       </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
         <v>154.28</v>
       </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2365,9 +1915,7 @@
           <t>2017-09</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>44.63</v>
       </c>
@@ -2380,41 +1928,27 @@
       <c r="F34" t="n">
         <v>0.9</v>
       </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="inlineStr"/>
+        <v>47.06</v>
+      </c>
+      <c r="I34" t="n">
+        <v>10.9</v>
+      </c>
       <c r="J34" t="n">
-        <v>47.06</v>
-      </c>
-      <c r="K34" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="L34" t="n">
         <v>6.220000000000001</v>
       </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
         <v>681.61</v>
       </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2422,9 +1956,7 @@
           <t>2017-10</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>51.78</v>
       </c>
@@ -2437,41 +1969,29 @@
       <c r="F35" t="n">
         <v>7.58</v>
       </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="inlineStr"/>
+        <v>25.46</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.4</v>
+      </c>
       <c r="J35" t="n">
-        <v>25.46</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1.4</v>
-      </c>
+        <v>20.28</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
-        <v>20.28</v>
+        <v>13.17</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="O35" t="n">
         <v>315.5700000000001</v>
       </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2494,41 +2014,29 @@
       <c r="F36" t="n">
         <v>1.85</v>
       </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="inlineStr"/>
+        <v>49.94</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3.13</v>
+      </c>
       <c r="J36" t="n">
-        <v>49.94</v>
-      </c>
-      <c r="K36" t="n">
-        <v>3.13</v>
-      </c>
+        <v>11.12</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
-        <v>11.12</v>
+        <v>330.27</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>330.27</v>
-      </c>
-      <c r="O36" t="n">
         <v>333.96</v>
       </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2551,41 +2059,33 @@
       <c r="F37" t="n">
         <v>13.27</v>
       </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="inlineStr"/>
+        <v>14.21</v>
+      </c>
+      <c r="I37" t="n">
+        <v>15.25</v>
+      </c>
       <c r="J37" t="n">
-        <v>14.21</v>
+        <v>48.41</v>
       </c>
       <c r="K37" t="n">
-        <v>15.25</v>
+        <v>0.75</v>
       </c>
       <c r="L37" t="n">
-        <v>48.41</v>
+        <v>463.39</v>
       </c>
       <c r="M37" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N37" t="n">
-        <v>463.39</v>
-      </c>
-      <c r="O37" t="n">
         <v>421.2</v>
       </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
+      <c r="Q37" t="n">
+        <v>1.01</v>
+      </c>
       <c r="R37" t="inlineStr"/>
-      <c r="S37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2593,9 +2093,7 @@
           <t>2018-01</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>115.7</v>
       </c>
@@ -2608,41 +2106,31 @@
       <c r="F38" t="n">
         <v>0.5</v>
       </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="inlineStr"/>
+        <v>57.3</v>
+      </c>
+      <c r="I38" t="n">
+        <v>4</v>
+      </c>
       <c r="J38" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="K38" t="n">
-        <v>4</v>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
-        <v>0.75</v>
+        <v>248.28</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>248.28</v>
-      </c>
-      <c r="O38" t="n">
         <v>175.89</v>
       </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
+      <c r="Q38" t="n">
+        <v>0.8</v>
+      </c>
       <c r="R38" t="inlineStr"/>
-      <c r="S38" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2650,9 +2138,7 @@
           <t>2018-02</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
         <v>69.40000000000001</v>
       </c>
@@ -2665,41 +2151,31 @@
       <c r="F39" t="n">
         <v>0.6</v>
       </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="inlineStr"/>
+        <v>34.65</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3</v>
+      </c>
       <c r="J39" t="n">
-        <v>34.65</v>
+        <v>0.84</v>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="L39" t="n">
-        <v>0.84</v>
+        <v>240.14</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N39" t="n">
-        <v>240.14</v>
-      </c>
-      <c r="O39" t="n">
         <v>279.16</v>
       </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2722,41 +2198,29 @@
       <c r="F40" t="n">
         <v>1.27</v>
       </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="inlineStr"/>
+        <v>41.43</v>
+      </c>
+      <c r="I40" t="n">
+        <v>4.27</v>
+      </c>
       <c r="J40" t="n">
-        <v>41.43</v>
-      </c>
-      <c r="K40" t="n">
-        <v>4.27</v>
-      </c>
+        <v>8.049999999999999</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
-        <v>8.049999999999999</v>
+        <v>253.15</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>253.15</v>
-      </c>
-      <c r="O40" t="n">
         <v>33.32</v>
       </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2764,56 +2228,40 @@
           <t>2018-04</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
         <v>130.17</v>
       </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
         <v>159.5</v>
       </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="inlineStr"/>
+        <v>22.4</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.9299999999999999</v>
+      </c>
       <c r="J41" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0.9299999999999999</v>
-      </c>
+        <v>9.279999999999999</v>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
-        <v>9.279999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O41" t="n">
         <v>131.1</v>
       </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
+      <c r="Q41" t="n">
+        <v>0.74</v>
+      </c>
       <c r="R41" t="inlineStr"/>
-      <c r="S41" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2836,41 +2284,29 @@
       <c r="F42" t="n">
         <v>0.5</v>
       </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="inlineStr"/>
+        <v>8.210000000000001</v>
+      </c>
+      <c r="I42" t="n">
+        <v>13.25</v>
+      </c>
       <c r="J42" t="n">
-        <v>8.210000000000001</v>
-      </c>
-      <c r="K42" t="n">
-        <v>13.25</v>
-      </c>
+        <v>3.89</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
-        <v>3.89</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O42" t="n">
         <v>134.59</v>
       </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2893,43 +2329,29 @@
       <c r="F43" t="n">
         <v>1.7</v>
       </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>17.51</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>55.23</v>
       </c>
       <c r="J43" t="n">
-        <v>17.51</v>
+        <v>4.6</v>
       </c>
       <c r="K43" t="n">
-        <v>55.23</v>
-      </c>
-      <c r="L43" t="n">
-        <v>4.6</v>
-      </c>
+        <v>0.37</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
         <v>248.32</v>
       </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
         <v>141.3</v>
       </c>
     </row>
@@ -2939,9 +2361,7 @@
           <t>2018-07</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
         <v>21.76</v>
       </c>
@@ -2951,46 +2371,30 @@
       <c r="E44" t="n">
         <v>60.01</v>
       </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="K44" t="n">
-        <v>1.1</v>
-      </c>
+        <v>0.37</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
-        <v>0.37</v>
+        <v>2.2</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O44" t="n">
         <v>166.25</v>
       </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
         <v>34.2</v>
       </c>
     </row>
@@ -3000,9 +2404,7 @@
           <t>2018-08</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
         <v>7.19</v>
       </c>
@@ -3012,46 +2414,32 @@
       <c r="E45" t="n">
         <v>78.09999999999999</v>
       </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>9.280000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
-        <v>9.280000000000001</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0.7</v>
-      </c>
+        <v>1.01</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O45" t="n">
         <v>153.3</v>
       </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
+      <c r="Q45" t="n">
+        <v>0.3</v>
+      </c>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
         <v>215.9</v>
       </c>
     </row>
@@ -3061,9 +2449,7 @@
           <t>2018-09</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>0</v>
-      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
         <v>45.97</v>
       </c>
@@ -3076,43 +2462,29 @@
       <c r="F46" t="n">
         <v>3.54</v>
       </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>49.19</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J46" t="n">
-        <v>49.19</v>
-      </c>
-      <c r="K46" t="n">
-        <v>12</v>
-      </c>
+        <v>6.81</v>
+      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
-        <v>6.81</v>
+        <v>4.6</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O46" t="n">
         <v>657.1900000000001</v>
       </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
         <v>84.8</v>
       </c>
     </row>
@@ -3122,9 +2494,7 @@
           <t>2018-10</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>0</v>
-      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
         <v>55.48</v>
       </c>
@@ -3137,43 +2507,29 @@
       <c r="F47" t="n">
         <v>3.01</v>
       </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>27.05</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="J47" t="n">
-        <v>27.05</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2.15</v>
-      </c>
+        <v>4.92</v>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
-        <v>4.92</v>
+        <v>12.74</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>12.74</v>
-      </c>
-      <c r="O47" t="n">
         <v>273.26</v>
       </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
         <v>141.8</v>
       </c>
     </row>
@@ -3183,58 +2539,40 @@
           <t>2018-11</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>0</v>
-      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
         <v>252.68</v>
       </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
         <v>355.05</v>
       </c>
       <c r="F48" t="n">
         <v>11.51</v>
       </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>47.27</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="J48" t="n">
-        <v>47.27</v>
-      </c>
-      <c r="K48" t="n">
-        <v>3.03</v>
-      </c>
+        <v>4.62</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
-        <v>4.62</v>
+        <v>332.45</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>332.45</v>
-      </c>
-      <c r="O48" t="n">
         <v>342.5599999999999</v>
       </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
         <v>217.02</v>
       </c>
     </row>
@@ -3259,43 +2597,33 @@
       <c r="F49" t="n">
         <v>21.95</v>
       </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>13.65</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>18.1</v>
       </c>
       <c r="J49" t="n">
-        <v>13.65</v>
+        <v>29.53</v>
       </c>
       <c r="K49" t="n">
-        <v>18.1</v>
+        <v>0.37</v>
       </c>
       <c r="L49" t="n">
-        <v>29.53</v>
+        <v>569.9300000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="N49" t="n">
-        <v>569.9300000000001</v>
-      </c>
-      <c r="O49" t="n">
         <v>424.8</v>
       </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
+      <c r="Q49" t="n">
+        <v>0.38</v>
+      </c>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
         <v>352.98</v>
       </c>
     </row>
@@ -3305,9 +2633,7 @@
           <t>2019-01</t>
         </is>
       </c>
-      <c r="B50" t="n">
-        <v>0</v>
-      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
         <v>117.94</v>
       </c>
@@ -3320,43 +2646,31 @@
       <c r="F50" t="n">
         <v>0.9</v>
       </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>60.22</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="J50" t="n">
-        <v>60.22</v>
-      </c>
-      <c r="K50" t="n">
-        <v>5.3</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="n">
-        <v>1.2</v>
+        <v>260.68</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>260.68</v>
-      </c>
-      <c r="O50" t="n">
         <v>177.04</v>
       </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
+      <c r="Q50" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
         <v>85.5</v>
       </c>
     </row>
@@ -3366,9 +2680,7 @@
           <t>2019-02</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>0</v>
-      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
         <v>70.37</v>
       </c>
@@ -3378,46 +2690,32 @@
       <c r="E51" t="n">
         <v>165.05</v>
       </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>35.19</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="J51" t="n">
-        <v>35.19</v>
-      </c>
-      <c r="K51" t="n">
-        <v>4.1</v>
-      </c>
+        <v>4.43</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="n">
-        <v>4.43</v>
+        <v>253.96</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>253.96</v>
-      </c>
-      <c r="O51" t="n">
         <v>274.84</v>
       </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
+      <c r="R51" t="n">
+        <v>0.4</v>
+      </c>
       <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U51" t="n">
         <v>76.90000000000001</v>
       </c>
     </row>
@@ -3427,9 +2725,7 @@
           <t>2019-03</t>
         </is>
       </c>
-      <c r="B52" t="n">
-        <v>0</v>
-      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
         <v>385.75</v>
       </c>
@@ -3442,43 +2738,31 @@
       <c r="F52" t="n">
         <v>0.75</v>
       </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>42.8</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="J52" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="K52" t="n">
-        <v>4.48</v>
-      </c>
+        <v>7.07</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="n">
-        <v>7.07</v>
+        <v>261.98</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>261.98</v>
-      </c>
-      <c r="O52" t="n">
         <v>37.12</v>
       </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>1</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
         <v>116.4</v>
       </c>
     </row>
@@ -3503,43 +2787,29 @@
       <c r="F53" t="n">
         <v>4.56</v>
       </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>22.22</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="J53" t="n">
-        <v>22.22</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0.43</v>
-      </c>
+        <v>2.83</v>
+      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="n">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="O53" t="n">
         <v>85.78</v>
       </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
         <v>95.43000000000001</v>
       </c>
     </row>
@@ -3549,9 +2819,7 @@
           <t>2019-05</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>0</v>
-      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
         <v>218.45</v>
       </c>
@@ -3564,43 +2832,31 @@
       <c r="F54" t="n">
         <v>4.5</v>
       </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>10.21</v>
       </c>
       <c r="J54" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="K54" t="n">
-        <v>10.21</v>
-      </c>
+        <v>9.5</v>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="n">
-        <v>9.5</v>
+        <v>0.7</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O54" t="n">
         <v>144.26</v>
       </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
+      <c r="Q54" t="n">
+        <v>0.9399999999999999</v>
+      </c>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
         <v>108.7</v>
       </c>
     </row>
@@ -3626,42 +2882,32 @@
         <v>3.2</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="H55" t="n">
-        <v>1.85</v>
+        <v>18.54</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="J55" t="n">
-        <v>18.54</v>
+        <v>4.18</v>
       </c>
       <c r="K55" t="n">
-        <v>83.09999999999999</v>
+        <v>0.41</v>
       </c>
       <c r="L55" t="n">
-        <v>4.18</v>
+        <v>2.7</v>
       </c>
       <c r="M55" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="N55" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O55" t="n">
         <v>248.68</v>
       </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
         <v>123.4</v>
       </c>
     </row>
@@ -3671,9 +2917,7 @@
           <t>2019-07</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>0</v>
-      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
         <v>21.78</v>
       </c>
@@ -3686,43 +2930,27 @@
       <c r="F56" t="n">
         <v>0.4</v>
       </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>17.25</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>17.25</v>
-      </c>
-      <c r="K56" t="n">
         <v>4.4</v>
       </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O56" t="n">
         <v>158.02</v>
       </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
         <v>48</v>
       </c>
     </row>
@@ -3738,52 +2966,36 @@
       <c r="C57" t="n">
         <v>7.2</v>
       </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
         <v>93.69999999999999</v>
       </c>
       <c r="F57" t="n">
         <v>8.4</v>
       </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>9.58</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>9.58</v>
-      </c>
-      <c r="K57" t="n">
-        <v>9.619999999999999</v>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="n">
-        <v>0.75</v>
+        <v>1.7</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O57" t="n">
         <v>156.03</v>
       </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
         <v>231.9</v>
       </c>
     </row>
@@ -3793,9 +3005,7 @@
           <t>2019-09</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>0</v>
-      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
         <v>47.06</v>
       </c>
@@ -3808,43 +3018,29 @@
       <c r="F58" t="n">
         <v>5.4</v>
       </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>49.37</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>17.2</v>
       </c>
       <c r="J58" t="n">
-        <v>49.37</v>
-      </c>
-      <c r="K58" t="n">
-        <v>17.2</v>
-      </c>
+        <v>7.67</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="n">
-        <v>7.67</v>
+        <v>2.23</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="O58" t="n">
         <v>656.21</v>
       </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
         <v>94.7</v>
       </c>
     </row>
@@ -3854,9 +3050,7 @@
           <t>2019-10</t>
         </is>
       </c>
-      <c r="B59" t="n">
-        <v>0</v>
-      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
         <v>58.02</v>
       </c>
@@ -3869,43 +3063,27 @@
       <c r="F59" t="n">
         <v>0.5</v>
       </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>28.04</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="n">
-        <v>28.04</v>
-      </c>
-      <c r="K59" t="n">
         <v>7.88</v>
       </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>15.38</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>15.38</v>
-      </c>
-      <c r="O59" t="n">
         <v>277.25</v>
       </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
         <v>141.51</v>
       </c>
     </row>
@@ -3915,9 +3093,7 @@
           <t>2019-11</t>
         </is>
       </c>
-      <c r="B60" t="n">
-        <v>0</v>
-      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
         <v>257.54</v>
       </c>
@@ -3930,43 +3106,29 @@
       <c r="F60" t="n">
         <v>2.3</v>
       </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>47.78999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="J60" t="n">
-        <v>47.78999999999999</v>
-      </c>
-      <c r="K60" t="n">
-        <v>19.8</v>
-      </c>
+        <v>0.78</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="n">
-        <v>0.78</v>
+        <v>340.24</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>340.24</v>
-      </c>
-      <c r="O60" t="n">
         <v>320.25</v>
       </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
         <v>227.36</v>
       </c>
     </row>
@@ -3991,43 +3153,29 @@
       <c r="F61" t="n">
         <v>17.77</v>
       </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="J61" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="K61" t="n">
-        <v>30.8</v>
-      </c>
+        <v>32.83</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="n">
-        <v>32.83</v>
+        <v>507.95</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
-        <v>507.95</v>
-      </c>
-      <c r="O61" t="n">
         <v>419.08</v>
       </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
         <v>468.13</v>
       </c>
     </row>
@@ -4037,9 +3185,7 @@
           <t>2020-01</t>
         </is>
       </c>
-      <c r="B62" t="n">
-        <v>0</v>
-      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
         <v>119.8</v>
       </c>
@@ -4049,46 +3195,32 @@
       <c r="E62" t="n">
         <v>293.4</v>
       </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>61.7</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="J62" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="K62" t="n">
-        <v>5.7</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="n">
-        <v>0.5</v>
+        <v>272.42</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
-        <v>272.42</v>
-      </c>
-      <c r="O62" t="n">
         <v>172.6</v>
       </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
+      <c r="Q62" t="n">
+        <v>0.43</v>
+      </c>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
         <v>89.19999999999999</v>
       </c>
     </row>
@@ -4098,9 +3230,7 @@
           <t>2020-02</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>0</v>
-      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
         <v>71.30000000000001</v>
       </c>
@@ -4113,43 +3243,31 @@
       <c r="F63" t="n">
         <v>0.6</v>
       </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>35.8</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="K63" t="n">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="n">
-        <v>4</v>
+        <v>259.5</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="n">
-        <v>259.5</v>
-      </c>
-      <c r="O63" t="n">
         <v>276.93</v>
       </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
+      <c r="R63" t="n">
+        <v>0.4</v>
+      </c>
       <c r="S63" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U63" t="n">
         <v>77.2</v>
       </c>
     </row>
@@ -4159,9 +3277,7 @@
           <t>2020-03</t>
         </is>
       </c>
-      <c r="B64" t="n">
-        <v>0</v>
-      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
         <v>396.9</v>
       </c>
@@ -4174,43 +3290,29 @@
       <c r="F64" t="n">
         <v>0.6</v>
       </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>43.2</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>12.3</v>
       </c>
       <c r="J64" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="K64" t="n">
-        <v>12.3</v>
-      </c>
+        <v>9.100000000000001</v>
+      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="n">
-        <v>9.100000000000001</v>
+        <v>273.16</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="n">
-        <v>273.16</v>
-      </c>
-      <c r="O64" t="n">
         <v>37.3</v>
       </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
         <v>122</v>
       </c>
     </row>
@@ -4220,58 +3322,42 @@
           <t>2020-04</t>
         </is>
       </c>
-      <c r="B65" t="n">
-        <v>0</v>
-      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
         <v>121.8</v>
       </c>
-      <c r="D65" t="n">
-        <v>0</v>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
         <v>143.6</v>
       </c>
       <c r="F65" t="n">
         <v>2.7</v>
       </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>25.1</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="J65" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="K65" t="n">
-        <v>2.7</v>
-      </c>
+        <v>3.2</v>
+      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="n">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="O65" t="n">
         <v>93.27</v>
       </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="n">
-        <v>1</v>
-      </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="n">
         <v>100.3</v>
       </c>
     </row>
@@ -4281,9 +3367,7 @@
           <t>2020-05</t>
         </is>
       </c>
-      <c r="B66" t="n">
-        <v>0</v>
-      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
         <v>228.1</v>
       </c>
@@ -4293,46 +3377,30 @@
       <c r="E66" t="n">
         <v>405.8</v>
       </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>4.800000000000001</v>
       </c>
       <c r="J66" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="K66" t="n">
-        <v>4.800000000000001</v>
-      </c>
+        <v>10.8</v>
+      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="n">
-        <v>10.8</v>
+        <v>0.45</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O66" t="n">
         <v>139.48</v>
       </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
         <v>113</v>
       </c>
     </row>
@@ -4357,43 +3425,29 @@
       <c r="F67" t="n">
         <v>3.1</v>
       </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>18.6</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>44.9</v>
       </c>
       <c r="J67" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="K67" t="n">
-        <v>44.9</v>
-      </c>
+        <v>5.5</v>
+      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="n">
-        <v>5.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="O67" t="n">
         <v>249.03</v>
       </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" t="n">
         <v>101.9</v>
       </c>
     </row>
@@ -4403,9 +3457,7 @@
           <t>2020-07</t>
         </is>
       </c>
-      <c r="B68" t="n">
-        <v>0</v>
-      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
         <v>21.9</v>
       </c>
@@ -4415,46 +3467,28 @@
       <c r="E68" t="n">
         <v>88.5</v>
       </c>
-      <c r="F68" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>17.1</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="K68" t="n">
         <v>4.4</v>
       </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O68" t="n">
         <v>158.4</v>
       </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" t="n">
         <v>74.5</v>
       </c>
     </row>
@@ -4464,9 +3498,7 @@
           <t>2020-08</t>
         </is>
       </c>
-      <c r="B69" t="n">
-        <v>0</v>
-      </c>
+      <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
         <v>7.2</v>
       </c>
@@ -4479,43 +3511,27 @@
       <c r="F69" t="n">
         <v>0.6</v>
       </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="K69" t="n">
         <v>10.6</v>
       </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O69" t="n">
         <v>152.9</v>
       </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" t="n">
         <v>236.5</v>
       </c>
     </row>
@@ -4525,9 +3541,7 @@
           <t>2020-09</t>
         </is>
       </c>
-      <c r="B70" t="n">
-        <v>0</v>
-      </c>
+      <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
         <v>63</v>
       </c>
@@ -4541,42 +3555,30 @@
         <v>5.85</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="H70" t="n">
-        <v>2.11</v>
+        <v>51.04</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>22.4</v>
       </c>
       <c r="J70" t="n">
-        <v>51.04</v>
-      </c>
-      <c r="K70" t="n">
-        <v>22.4</v>
-      </c>
+        <v>6.4</v>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="n">
-        <v>6.4</v>
+        <v>12.59</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="n">
-        <v>12.59</v>
-      </c>
-      <c r="O70" t="n">
         <v>654.03</v>
       </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" t="n">
         <v>112.7</v>
       </c>
     </row>
@@ -4586,9 +3588,7 @@
           <t>2020-10</t>
         </is>
       </c>
-      <c r="B71" t="n">
-        <v>0</v>
-      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
         <v>59.9</v>
       </c>
@@ -4601,43 +3601,29 @@
       <c r="F71" t="n">
         <v>3.15</v>
       </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>28.69</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>28.69</v>
-      </c>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="n">
-        <v>9.699999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>27.37</v>
       </c>
       <c r="M71" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N71" t="n">
-        <v>27.37</v>
-      </c>
-      <c r="O71" t="n">
         <v>280.02</v>
       </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="n">
         <v>168.4</v>
       </c>
     </row>
@@ -4647,9 +3633,7 @@
           <t>2020-11</t>
         </is>
       </c>
-      <c r="B72" t="n">
-        <v>0</v>
-      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
         <v>260.2</v>
       </c>
@@ -4662,43 +3646,31 @@
       <c r="F72" t="n">
         <v>3.5</v>
       </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>47.8</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="K72" t="n">
-        <v>1.4</v>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="n">
-        <v>0.8</v>
+        <v>343.13</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="n">
-        <v>343.13</v>
-      </c>
-      <c r="O72" t="n">
         <v>321.7</v>
       </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
+      <c r="Q72" t="n">
+        <v>1.53</v>
+      </c>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="T72" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" t="n">
         <v>287.62</v>
       </c>
     </row>
@@ -4708,9 +3680,7 @@
           <t>2020-12</t>
         </is>
       </c>
-      <c r="B73" t="n">
-        <v>0</v>
-      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
         <v>552.1</v>
       </c>
@@ -4723,43 +3693,31 @@
       <c r="F73" t="n">
         <v>2.8</v>
       </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>17.7</v>
       </c>
       <c r="J73" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K73" t="n">
-        <v>17.7</v>
-      </c>
+        <v>31.1</v>
+      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="n">
-        <v>31.1</v>
+        <v>601.98</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
-        <v>601.98</v>
-      </c>
-      <c r="O73" t="n">
         <v>429.15</v>
       </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
+      <c r="Q73" t="n">
+        <v>5.7</v>
+      </c>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="T73" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" t="n">
         <v>420.94</v>
       </c>
     </row>
@@ -4769,9 +3727,7 @@
           <t>2021-01</t>
         </is>
       </c>
-      <c r="B74" t="n">
-        <v>0</v>
-      </c>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
         <v>121.6</v>
       </c>
@@ -4781,46 +3737,30 @@
       <c r="E74" t="n">
         <v>292.76</v>
       </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>62.90000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J74" t="n">
-        <v>62.90000000000001</v>
-      </c>
-      <c r="K74" t="n">
-        <v>2.1</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="n">
-        <v>0.5</v>
+        <v>306.99</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" t="n">
-        <v>306.99</v>
-      </c>
-      <c r="O74" t="n">
         <v>173.56</v>
       </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>0</v>
-      </c>
-      <c r="T74" t="n">
-        <v>0</v>
-      </c>
-      <c r="U74" t="n">
         <v>92.09999999999999</v>
       </c>
     </row>
@@ -4830,9 +3770,7 @@
           <t>2021-02</t>
         </is>
       </c>
-      <c r="B75" t="n">
-        <v>0</v>
-      </c>
+      <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
         <v>71.8</v>
       </c>
@@ -4842,46 +3780,30 @@
       <c r="E75" t="n">
         <v>188.3</v>
       </c>
-      <c r="F75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="n">
-        <v>0</v>
-      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>36.6</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="J75" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="K75" t="n">
-        <v>9.5</v>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="n">
-        <v>0.8</v>
+        <v>344</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" t="n">
-        <v>344</v>
-      </c>
-      <c r="O75" t="n">
         <v>277.5</v>
       </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" t="n">
-        <v>0</v>
-      </c>
-      <c r="U75" t="n">
         <v>79.7</v>
       </c>
     </row>
@@ -4891,9 +3813,7 @@
           <t>2021-03</t>
         </is>
       </c>
-      <c r="B76" t="n">
-        <v>0</v>
-      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
         <v>398.4</v>
       </c>
@@ -4906,43 +3826,29 @@
       <c r="F76" t="n">
         <v>0.9</v>
       </c>
-      <c r="G76" t="n">
-        <v>0</v>
-      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>44.1</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="J76" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="K76" t="n">
-        <v>4.9</v>
-      </c>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="n">
-        <v>9.199999999999999</v>
+        <v>348.5</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="n">
-        <v>348.5</v>
-      </c>
-      <c r="O76" t="n">
         <v>40.85</v>
       </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" t="n">
-        <v>0</v>
-      </c>
-      <c r="U76" t="n">
         <v>126.73</v>
       </c>
     </row>
@@ -4952,9 +3858,7 @@
           <t>2021-04</t>
         </is>
       </c>
-      <c r="B77" t="n">
-        <v>0</v>
-      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
         <v>128.5</v>
       </c>
@@ -4967,43 +3871,29 @@
       <c r="F77" t="n">
         <v>1.35</v>
       </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>22.8</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="K77" t="n">
-        <v>1</v>
-      </c>
+        <v>2.4</v>
+      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="n">
-        <v>2.4</v>
+        <v>46.7</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="O77" t="n">
         <v>87</v>
       </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" t="n">
         <v>103.6</v>
       </c>
     </row>
@@ -5013,9 +3903,7 @@
           <t>2021-05</t>
         </is>
       </c>
-      <c r="B78" t="n">
-        <v>0</v>
-      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
         <v>228.8</v>
       </c>
@@ -5025,46 +3913,30 @@
       <c r="E78" t="n">
         <v>421.44</v>
       </c>
-      <c r="F78" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0</v>
-      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J78" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="K78" t="n">
-        <v>6</v>
-      </c>
+        <v>10.2</v>
+      </c>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="n">
-        <v>10.2</v>
+        <v>3.29</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="O78" t="n">
         <v>134.3</v>
       </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" t="n">
         <v>116.8</v>
       </c>
     </row>
@@ -5074,9 +3946,7 @@
           <t>2021-06</t>
         </is>
       </c>
-      <c r="B79" t="n">
-        <v>0</v>
-      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
         <v>13.1</v>
       </c>
@@ -5089,43 +3959,29 @@
       <c r="F79" t="n">
         <v>3.3</v>
       </c>
-      <c r="G79" t="n">
-        <v>0</v>
-      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>45.7</v>
       </c>
       <c r="J79" t="n">
-        <v>19</v>
-      </c>
-      <c r="K79" t="n">
-        <v>45.7</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O79" t="n">
         <v>312.9</v>
       </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" t="n">
         <v>110.9</v>
       </c>
     </row>
@@ -5150,43 +4006,31 @@
       <c r="F80" t="n">
         <v>0.5</v>
       </c>
-      <c r="G80" t="n">
-        <v>0</v>
-      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" t="n">
-        <v>17.5</v>
-      </c>
+        <v>0.4</v>
+      </c>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M80" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O80" t="n">
         <v>160.15</v>
       </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
+      <c r="R80" t="n">
+        <v>0.7</v>
+      </c>
       <c r="S80" t="n">
-        <v>0</v>
-      </c>
-      <c r="T80" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="U80" t="n">
         <v>49.8</v>
       </c>
     </row>
@@ -5196,9 +4040,7 @@
           <t>2021-08</t>
         </is>
       </c>
-      <c r="B81" t="n">
-        <v>0</v>
-      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
         <v>7.2</v>
       </c>
@@ -5208,46 +4050,28 @@
       <c r="E81" t="n">
         <v>97.53999999999999</v>
       </c>
-      <c r="F81" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" t="n">
-        <v>0</v>
-      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="K81" t="n">
         <v>7.5</v>
       </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O81" t="n">
         <v>152.9</v>
       </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" t="n">
-        <v>0</v>
-      </c>
-      <c r="U81" t="n">
         <v>267.26</v>
       </c>
     </row>
@@ -5257,9 +4081,7 @@
           <t>2021-09</t>
         </is>
       </c>
-      <c r="B82" t="n">
-        <v>0</v>
-      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
         <v>63.90000000000001</v>
       </c>
@@ -5272,43 +4094,31 @@
       <c r="F82" t="n">
         <v>7.6</v>
       </c>
-      <c r="G82" t="n">
-        <v>0</v>
-      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>22.7</v>
       </c>
       <c r="J82" t="n">
-        <v>53</v>
-      </c>
-      <c r="K82" t="n">
-        <v>22.7</v>
-      </c>
+        <v>7.8</v>
+      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="n">
-        <v>7.8</v>
+        <v>8.85</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="n">
-        <v>8.85</v>
-      </c>
-      <c r="O82" t="n">
         <v>646.96</v>
       </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
+      <c r="R82" t="n">
+        <v>1.9</v>
+      </c>
       <c r="S82" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U82" t="n">
         <v>118.35</v>
       </c>
     </row>
@@ -5318,9 +4128,7 @@
           <t>2021-10</t>
         </is>
       </c>
-      <c r="B83" t="n">
-        <v>0</v>
-      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
         <v>61.90000000000001</v>
       </c>
@@ -5330,46 +4138,30 @@
       <c r="E83" t="n">
         <v>631.65</v>
       </c>
-      <c r="F83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" t="n">
-        <v>0</v>
-      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>27.1</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J83" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="K83" t="n">
-        <v>8.9</v>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="n">
-        <v>0.8</v>
+        <v>30.87</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="n">
-        <v>30.87</v>
-      </c>
-      <c r="O83" t="n">
         <v>275.4</v>
       </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="n">
-        <v>0</v>
-      </c>
-      <c r="T83" t="n">
-        <v>0</v>
-      </c>
-      <c r="U83" t="n">
         <v>151.1</v>
       </c>
     </row>
@@ -5379,9 +4171,7 @@
           <t>2021-11</t>
         </is>
       </c>
-      <c r="B84" t="n">
-        <v>0</v>
-      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
         <v>150.7</v>
       </c>
@@ -5394,43 +4184,31 @@
       <c r="F84" t="n">
         <v>2.2</v>
       </c>
-      <c r="G84" t="n">
-        <v>0</v>
-      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>48.4</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
-        <v>48.4</v>
+        <v>0.8</v>
       </c>
       <c r="K84" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="L84" t="n">
-        <v>0.8</v>
+        <v>370.76</v>
       </c>
       <c r="M84" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N84" t="n">
-        <v>370.76</v>
-      </c>
-      <c r="O84" t="n">
         <v>313</v>
       </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="n">
-        <v>0</v>
-      </c>
-      <c r="T84" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" t="n">
         <v>264.06</v>
       </c>
     </row>
@@ -5440,9 +4218,7 @@
           <t>2021-12</t>
         </is>
       </c>
-      <c r="B85" t="n">
-        <v>0</v>
-      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
         <v>554.9</v>
       </c>
@@ -5455,43 +4231,31 @@
       <c r="F85" t="n">
         <v>5.5</v>
       </c>
-      <c r="G85" t="n">
-        <v>0</v>
-      </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>14.28</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>17.9</v>
       </c>
       <c r="J85" t="n">
-        <v>14.28</v>
-      </c>
-      <c r="K85" t="n">
-        <v>17.9</v>
-      </c>
+        <v>25.5</v>
+      </c>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="n">
-        <v>25.5</v>
+        <v>659.8</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="n">
-        <v>659.8</v>
-      </c>
-      <c r="O85" t="n">
         <v>413.4</v>
       </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
+      <c r="R85" t="n">
+        <v>0.7</v>
+      </c>
       <c r="S85" t="n">
-        <v>0</v>
-      </c>
-      <c r="T85" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="U85" t="n">
         <v>437.97</v>
       </c>
     </row>
@@ -5501,9 +4265,7 @@
           <t>2022-01</t>
         </is>
       </c>
-      <c r="B86" t="n">
-        <v>0</v>
-      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
         <v>121.3</v>
       </c>
@@ -5513,46 +4275,30 @@
       <c r="E86" t="n">
         <v>286.67</v>
       </c>
-      <c r="F86" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" t="n">
-        <v>0</v>
-      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>63.7</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J86" t="n">
-        <v>63.7</v>
-      </c>
-      <c r="K86" t="n">
-        <v>2.6</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="n">
-        <v>0.5</v>
+        <v>333.29</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" t="n">
-        <v>333.29</v>
-      </c>
-      <c r="O86" t="n">
         <v>172.86</v>
       </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="n">
-        <v>0</v>
-      </c>
-      <c r="T86" t="n">
-        <v>0</v>
-      </c>
-      <c r="U86" t="n">
         <v>89.69999999999999</v>
       </c>
     </row>
@@ -5562,9 +4308,7 @@
           <t>2022-02</t>
         </is>
       </c>
-      <c r="B87" t="n">
-        <v>0</v>
-      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
         <v>73.3</v>
       </c>
@@ -5577,43 +4321,27 @@
       <c r="F87" t="n">
         <v>0.2</v>
       </c>
-      <c r="G87" t="n">
-        <v>0</v>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>36.6</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="K87" t="n">
         <v>12.4</v>
       </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>363.02</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="n">
-        <v>363.02</v>
-      </c>
-      <c r="O87" t="n">
         <v>276.42</v>
       </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="n">
-        <v>0</v>
-      </c>
-      <c r="T87" t="n">
-        <v>0</v>
-      </c>
-      <c r="U87" t="n">
         <v>81.34999999999999</v>
       </c>
     </row>
@@ -5623,9 +4351,7 @@
           <t>2022-03</t>
         </is>
       </c>
-      <c r="B88" t="n">
-        <v>0</v>
-      </c>
+      <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
         <v>404.2</v>
       </c>
@@ -5635,46 +4361,32 @@
       <c r="E88" t="n">
         <v>513.16</v>
       </c>
-      <c r="F88" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" t="n">
-        <v>0</v>
-      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J88" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="K88" t="n">
-        <v>7.1</v>
+        <v>1</v>
       </c>
       <c r="L88" t="n">
-        <v>10</v>
+        <v>337.7</v>
       </c>
       <c r="M88" t="n">
-        <v>1</v>
-      </c>
-      <c r="N88" t="n">
-        <v>337.7</v>
-      </c>
-      <c r="O88" t="n">
         <v>38.2</v>
       </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="n">
-        <v>0</v>
-      </c>
-      <c r="T88" t="n">
-        <v>0</v>
-      </c>
-      <c r="U88" t="n">
         <v>129.87</v>
       </c>
     </row>
@@ -5684,9 +4396,7 @@
           <t>2022-04</t>
         </is>
       </c>
-      <c r="B89" t="n">
-        <v>0</v>
-      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
         <v>128.7</v>
       </c>
@@ -5699,43 +4409,29 @@
       <c r="F89" t="n">
         <v>1</v>
       </c>
-      <c r="G89" t="n">
-        <v>0</v>
-      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>22.8</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J89" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="K89" t="n">
-        <v>1.5</v>
-      </c>
+        <v>2.4</v>
+      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="n">
-        <v>2.4</v>
+        <v>62.18</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="n">
-        <v>62.18</v>
-      </c>
-      <c r="O89" t="n">
         <v>87.46000000000001</v>
       </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" t="n">
         <v>110.81</v>
       </c>
     </row>
@@ -5745,9 +4441,7 @@
           <t>2022-05</t>
         </is>
       </c>
-      <c r="B90" t="n">
-        <v>0</v>
-      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
         <v>234.9</v>
       </c>
@@ -5757,46 +4451,30 @@
       <c r="E90" t="n">
         <v>402.1</v>
       </c>
-      <c r="F90" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" t="n">
-        <v>0</v>
-      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="J90" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="K90" t="n">
-        <v>11.8</v>
-      </c>
+        <v>10.2</v>
+      </c>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="n">
-        <v>10.2</v>
+        <v>4.94</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="O90" t="n">
         <v>135.22</v>
       </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" t="n">
         <v>116.51</v>
       </c>
     </row>
@@ -5806,9 +4484,7 @@
           <t>2022-06</t>
         </is>
       </c>
-      <c r="B91" t="n">
-        <v>0</v>
-      </c>
+      <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
         <v>13.6</v>
       </c>
@@ -5818,52 +4494,36 @@
       <c r="E91" t="n">
         <v>432.22</v>
       </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="n">
-        <v>0</v>
-      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>50.7</v>
       </c>
       <c r="J91" t="n">
-        <v>19.2</v>
+        <v>7.6</v>
       </c>
       <c r="K91" t="n">
-        <v>50.7</v>
+        <v>5</v>
       </c>
       <c r="L91" t="n">
-        <v>7.6</v>
+        <v>2</v>
       </c>
       <c r="M91" t="n">
-        <v>5</v>
+        <v>314.2</v>
       </c>
       <c r="N91" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="O91" t="n">
-        <v>314.2</v>
-      </c>
-      <c r="P91" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="Q91" t="n">
         <v>1.3</v>
       </c>
-      <c r="R91" t="n">
-        <v>0</v>
-      </c>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
       <c r="S91" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" t="n">
-        <v>0</v>
-      </c>
-      <c r="U91" t="n">
         <v>110.21</v>
       </c>
     </row>
@@ -5873,9 +4533,7 @@
           <t>2022-07</t>
         </is>
       </c>
-      <c r="B92" t="n">
-        <v>0</v>
-      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
         <v>23.6</v>
       </c>
@@ -5885,52 +4543,28 @@
       <c r="E92" t="n">
         <v>121.53</v>
       </c>
-      <c r="F92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" t="n">
-        <v>0</v>
-      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="K92" t="n">
         <v>0.4</v>
       </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" t="n">
-        <v>2</v>
-      </c>
-      <c r="O92" t="n">
         <v>162.06</v>
       </c>
-      <c r="P92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
       <c r="S92" t="n">
-        <v>0</v>
-      </c>
-      <c r="T92" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" t="n">
         <v>53</v>
       </c>
     </row>
@@ -5940,9 +4574,7 @@
           <t>2022-08</t>
         </is>
       </c>
-      <c r="B93" t="n">
-        <v>0</v>
-      </c>
+      <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
         <v>6.3</v>
       </c>
@@ -5952,52 +4584,28 @@
       <c r="E93" t="n">
         <v>126.2</v>
       </c>
-      <c r="F93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" t="n">
-        <v>0</v>
-      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="K93" t="n">
         <v>8.700000000000001</v>
       </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O93" t="n">
         <v>154.22</v>
       </c>
-      <c r="P93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
-      <c r="R93" t="n">
-        <v>0</v>
-      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
       <c r="S93" t="n">
-        <v>0</v>
-      </c>
-      <c r="T93" t="n">
-        <v>0</v>
-      </c>
-      <c r="U93" t="n">
         <v>248.4</v>
       </c>
     </row>
@@ -6007,9 +4615,7 @@
           <t>2022-09</t>
         </is>
       </c>
-      <c r="B94" t="n">
-        <v>0</v>
-      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
         <v>49.8</v>
       </c>
@@ -6019,52 +4625,32 @@
       <c r="E94" t="n">
         <v>637.5</v>
       </c>
-      <c r="F94" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" t="n">
-        <v>0</v>
-      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>53.1</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>22.4</v>
       </c>
       <c r="J94" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="K94" t="n">
-        <v>22.4</v>
-      </c>
+        <v>7.8</v>
+      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="n">
-        <v>7.8</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" t="n">
-        <v>9.050000000000001</v>
-      </c>
+        <v>652.8200000000001</v>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="O94" t="n">
-        <v>652.8200000000001</v>
-      </c>
-      <c r="P94" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q94" t="n">
         <v>0.9</v>
       </c>
-      <c r="R94" t="n">
-        <v>0</v>
-      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
       <c r="S94" t="n">
-        <v>0</v>
-      </c>
-      <c r="T94" t="n">
-        <v>0</v>
-      </c>
-      <c r="U94" t="n">
         <v>157.22</v>
       </c>
     </row>
@@ -6074,9 +4660,7 @@
           <t>2022-10</t>
         </is>
       </c>
-      <c r="B95" t="n">
-        <v>0</v>
-      </c>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
         <v>62.40000000000001</v>
       </c>
@@ -6086,52 +4670,30 @@
       <c r="E95" t="n">
         <v>651.7</v>
       </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="J95" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="K95" t="n">
-        <v>9.1</v>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="n">
-        <v>0.8</v>
+        <v>40.09999999999999</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="O95" t="n">
         <v>273.36</v>
       </c>
-      <c r="P95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
-      <c r="R95" t="n">
-        <v>0</v>
-      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
       <c r="S95" t="n">
-        <v>0</v>
-      </c>
-      <c r="T95" t="n">
-        <v>0</v>
-      </c>
-      <c r="U95" t="n">
         <v>169.62</v>
       </c>
     </row>
@@ -6141,9 +4703,7 @@
           <t>2022-11</t>
         </is>
       </c>
-      <c r="B96" t="n">
-        <v>0</v>
-      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
         <v>153.7</v>
       </c>
@@ -6156,49 +4716,31 @@
       <c r="F96" t="n">
         <v>0.3</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>50.84</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
-        <v>50.84</v>
-      </c>
-      <c r="K96" t="n">
-        <v>2</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="n">
-        <v>1.2</v>
+        <v>384.59</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>316.34</v>
       </c>
       <c r="N96" t="n">
-        <v>384.59</v>
-      </c>
-      <c r="O96" t="n">
-        <v>316.34</v>
-      </c>
-      <c r="P96" t="n">
         <v>5.7</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
-      <c r="R96" t="n">
-        <v>0</v>
-      </c>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
       <c r="S96" t="n">
-        <v>0</v>
-      </c>
-      <c r="T96" t="n">
-        <v>0</v>
-      </c>
-      <c r="U96" t="n">
         <v>272.22</v>
       </c>
     </row>
@@ -6208,9 +4750,7 @@
           <t>2022-12</t>
         </is>
       </c>
-      <c r="B97" t="n">
-        <v>0</v>
-      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
         <v>552.8000000000001</v>
       </c>
@@ -6223,49 +4763,37 @@
       <c r="F97" t="n">
         <v>1.7</v>
       </c>
-      <c r="G97" t="n">
-        <v>0</v>
-      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J97" t="n">
-        <v>12.8</v>
+        <v>25.2</v>
       </c>
       <c r="K97" t="n">
-        <v>19</v>
+        <v>1.5</v>
       </c>
       <c r="L97" t="n">
-        <v>25.2</v>
+        <v>734.26</v>
       </c>
       <c r="M97" t="n">
-        <v>1.5</v>
+        <v>411.24</v>
       </c>
       <c r="N97" t="n">
-        <v>734.26</v>
+        <v>24.4</v>
       </c>
       <c r="O97" t="n">
-        <v>411.24</v>
+        <v>5.7</v>
       </c>
       <c r="P97" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="R97" t="n">
         <v>0.4</v>
       </c>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
       <c r="S97" t="n">
-        <v>0</v>
-      </c>
-      <c r="T97" t="n">
-        <v>0</v>
-      </c>
-      <c r="U97" t="n">
         <v>432.6</v>
       </c>
     </row>
@@ -6275,9 +4803,7 @@
           <t>2023-01</t>
         </is>
       </c>
-      <c r="B98" t="n">
-        <v>0</v>
-      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
         <v>118.07</v>
       </c>
@@ -6287,52 +4813,30 @@
       <c r="E98" t="n">
         <v>307.85</v>
       </c>
-      <c r="F98" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" t="n">
-        <v>0</v>
-      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>108.21</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J98" t="n">
-        <v>108.21</v>
-      </c>
-      <c r="K98" t="n">
-        <v>2.6</v>
-      </c>
+        <v>0.51</v>
+      </c>
+      <c r="K98" t="inlineStr"/>
       <c r="L98" t="n">
-        <v>0.51</v>
+        <v>378.74</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" t="n">
-        <v>378.74</v>
-      </c>
-      <c r="O98" t="n">
         <v>171.02</v>
       </c>
-      <c r="P98" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
-      <c r="R98" t="n">
-        <v>0</v>
-      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
       <c r="S98" t="n">
-        <v>0</v>
-      </c>
-      <c r="T98" t="n">
-        <v>0</v>
-      </c>
-      <c r="U98" t="n">
         <v>90.01000000000001</v>
       </c>
     </row>
@@ -6354,52 +4858,30 @@
       <c r="E99" t="n">
         <v>200.59</v>
       </c>
-      <c r="F99" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" t="n">
-        <v>0</v>
-      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>31.59</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" t="n">
-        <v>31.59</v>
-      </c>
-      <c r="K99" t="n">
         <v>12.55</v>
       </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>414.84</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" t="n">
-        <v>414.84</v>
-      </c>
+        <v>295.85</v>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="O99" t="n">
-        <v>295.85</v>
-      </c>
-      <c r="P99" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" t="n">
         <v>0.25</v>
       </c>
-      <c r="R99" t="n">
-        <v>0</v>
-      </c>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
       <c r="S99" t="n">
-        <v>0</v>
-      </c>
-      <c r="T99" t="n">
-        <v>0</v>
-      </c>
-      <c r="U99" t="n">
         <v>85.56999999999999</v>
       </c>
     </row>
@@ -6409,9 +4891,7 @@
           <t>2023-03</t>
         </is>
       </c>
-      <c r="B100" t="n">
-        <v>0</v>
-      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
         <v>384.21</v>
       </c>
@@ -6421,52 +4901,32 @@
       <c r="E100" t="n">
         <v>466.6</v>
       </c>
-      <c r="F100" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" t="n">
-        <v>0</v>
-      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>57.56</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>9.92</v>
       </c>
       <c r="J100" t="n">
-        <v>57.56</v>
-      </c>
-      <c r="K100" t="n">
-        <v>9.92</v>
-      </c>
+        <v>8.73</v>
+      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="n">
-        <v>8.73</v>
+        <v>359.2</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" t="n">
-        <v>359.2</v>
-      </c>
+        <v>44.66</v>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="O100" t="n">
-        <v>44.66</v>
-      </c>
-      <c r="P100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" t="n">
         <v>12.77</v>
       </c>
-      <c r="R100" t="n">
-        <v>0</v>
-      </c>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
       <c r="S100" t="n">
-        <v>0</v>
-      </c>
-      <c r="T100" t="n">
-        <v>0</v>
-      </c>
-      <c r="U100" t="n">
         <v>111.57</v>
       </c>
     </row>
@@ -6476,9 +4936,7 @@
           <t>2023-04</t>
         </is>
       </c>
-      <c r="B101" t="n">
-        <v>0</v>
-      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
         <v>121.01</v>
       </c>
@@ -6491,49 +4949,29 @@
       <c r="F101" t="n">
         <v>0.4</v>
       </c>
-      <c r="G101" t="n">
-        <v>0</v>
-      </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>16.68</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="J101" t="n">
-        <v>16.68</v>
-      </c>
-      <c r="K101" t="n">
-        <v>1.52</v>
-      </c>
+        <v>1.98</v>
+      </c>
+      <c r="K101" t="inlineStr"/>
       <c r="L101" t="n">
-        <v>1.98</v>
+        <v>44.25</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" t="n">
-        <v>44.25</v>
-      </c>
-      <c r="O101" t="n">
         <v>94.34999999999999</v>
       </c>
-      <c r="P101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0</v>
-      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
       <c r="S101" t="n">
-        <v>0</v>
-      </c>
-      <c r="T101" t="n">
-        <v>0</v>
-      </c>
-      <c r="U101" t="n">
         <v>109.46</v>
       </c>
     </row>
@@ -6543,9 +4981,7 @@
           <t>2023-05</t>
         </is>
       </c>
-      <c r="B102" t="n">
-        <v>0</v>
-      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
         <v>223.46</v>
       </c>
@@ -6555,52 +4991,30 @@
       <c r="E102" t="n">
         <v>414.5600000000001</v>
       </c>
-      <c r="F102" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" t="n">
-        <v>0</v>
-      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>14.41</v>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J102" t="n">
-        <v>14.41</v>
-      </c>
-      <c r="K102" t="n">
-        <v>9.6</v>
-      </c>
+        <v>6.2</v>
+      </c>
+      <c r="K102" t="inlineStr"/>
       <c r="L102" t="n">
-        <v>6.2</v>
+        <v>2.5</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O102" t="n">
         <v>146.06</v>
       </c>
-      <c r="P102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" t="n">
-        <v>0</v>
-      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
       <c r="S102" t="n">
-        <v>0</v>
-      </c>
-      <c r="T102" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" t="n">
         <v>114.33</v>
       </c>
     </row>
@@ -6610,9 +5024,7 @@
           <t>2023-06</t>
         </is>
       </c>
-      <c r="B103" t="n">
-        <v>0</v>
-      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
         <v>11.76</v>
       </c>
@@ -6622,52 +5034,34 @@
       <c r="E103" t="n">
         <v>405.1899999999999</v>
       </c>
-      <c r="F103" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" t="n">
-        <v>0</v>
-      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>16.02</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>56.39</v>
       </c>
       <c r="J103" t="n">
-        <v>16.02</v>
-      </c>
-      <c r="K103" t="n">
-        <v>56.39</v>
-      </c>
+        <v>7.300000000000001</v>
+      </c>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="n">
-        <v>7.300000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>318.17</v>
       </c>
       <c r="N103" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="O103" t="n">
-        <v>318.17</v>
-      </c>
-      <c r="P103" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q103" t="n">
         <v>26.53</v>
       </c>
-      <c r="R103" t="n">
-        <v>0</v>
-      </c>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
       <c r="S103" t="n">
-        <v>0</v>
-      </c>
-      <c r="T103" t="n">
-        <v>0</v>
-      </c>
-      <c r="U103" t="n">
         <v>103.64</v>
       </c>
     </row>
@@ -6677,9 +5071,7 @@
           <t>2023-07</t>
         </is>
       </c>
-      <c r="B104" t="n">
-        <v>0</v>
-      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
         <v>21.39</v>
       </c>
@@ -6689,52 +5081,28 @@
       <c r="E104" t="n">
         <v>184.8</v>
       </c>
-      <c r="F104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" t="n">
-        <v>0</v>
-      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="K104" t="n">
         <v>0.55</v>
       </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O104" t="n">
         <v>164.87</v>
       </c>
-      <c r="P104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
-      <c r="R104" t="n">
-        <v>0</v>
-      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
       <c r="S104" t="n">
-        <v>0</v>
-      </c>
-      <c r="T104" t="n">
-        <v>0</v>
-      </c>
-      <c r="U104" t="n">
         <v>42.12</v>
       </c>
     </row>
@@ -6744,9 +5112,7 @@
           <t>2023-08</t>
         </is>
       </c>
-      <c r="B105" t="n">
-        <v>0</v>
-      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
         <v>5.52</v>
       </c>
@@ -6759,49 +5125,29 @@
       <c r="F105" t="n">
         <v>0.3</v>
       </c>
-      <c r="G105" t="n">
-        <v>0</v>
-      </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>10.73</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" t="n">
-        <v>10.73</v>
-      </c>
-      <c r="K105" t="n">
         <v>6.9</v>
       </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" t="n">
-        <v>3.25</v>
-      </c>
+        <v>155.14</v>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="O105" t="n">
-        <v>155.14</v>
-      </c>
-      <c r="P105" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q105" t="n">
         <v>4.22</v>
       </c>
-      <c r="R105" t="n">
-        <v>0</v>
-      </c>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
       <c r="S105" t="n">
-        <v>0</v>
-      </c>
-      <c r="T105" t="n">
-        <v>0</v>
-      </c>
-      <c r="U105" t="n">
         <v>181.83</v>
       </c>
     </row>
@@ -6811,9 +5157,7 @@
           <t>2023-09</t>
         </is>
       </c>
-      <c r="B106" t="n">
-        <v>0</v>
-      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
         <v>48.18</v>
       </c>
@@ -6823,52 +5167,34 @@
       <c r="E106" t="n">
         <v>717.92</v>
       </c>
-      <c r="F106" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" t="n">
-        <v>0</v>
-      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>95.97</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>30.35</v>
       </c>
       <c r="J106" t="n">
-        <v>95.97</v>
+        <v>7.97</v>
       </c>
       <c r="K106" t="n">
-        <v>30.35</v>
+        <v>0.2</v>
       </c>
       <c r="L106" t="n">
-        <v>7.97</v>
+        <v>7.44</v>
       </c>
       <c r="M106" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N106" t="n">
-        <v>7.44</v>
-      </c>
+        <v>645.52</v>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="O106" t="n">
-        <v>645.52</v>
-      </c>
-      <c r="P106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" t="n">
         <v>0.98</v>
       </c>
-      <c r="R106" t="n">
-        <v>0</v>
-      </c>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
       <c r="S106" t="n">
-        <v>0</v>
-      </c>
-      <c r="T106" t="n">
-        <v>0</v>
-      </c>
-      <c r="U106" t="n">
         <v>120.15</v>
       </c>
     </row>
@@ -6878,9 +5204,7 @@
           <t>2023-10</t>
         </is>
       </c>
-      <c r="B107" t="n">
-        <v>0</v>
-      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
         <v>61.39</v>
       </c>
@@ -6890,52 +5214,30 @@
       <c r="E107" t="n">
         <v>719.01</v>
       </c>
-      <c r="F107" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" t="n">
-        <v>0</v>
-      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>22.63</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>13.07</v>
       </c>
       <c r="J107" t="n">
-        <v>22.63</v>
-      </c>
-      <c r="K107" t="n">
-        <v>13.07</v>
-      </c>
+        <v>0.66</v>
+      </c>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" t="n">
-        <v>0.66</v>
+        <v>41.19</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" t="n">
-        <v>41.19</v>
-      </c>
-      <c r="O107" t="n">
         <v>277.77</v>
       </c>
-      <c r="P107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
-      <c r="R107" t="n">
-        <v>0</v>
-      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
       <c r="S107" t="n">
-        <v>0</v>
-      </c>
-      <c r="T107" t="n">
-        <v>0</v>
-      </c>
-      <c r="U107" t="n">
         <v>118.71</v>
       </c>
     </row>
@@ -6945,9 +5247,7 @@
           <t>2023-11</t>
         </is>
       </c>
-      <c r="B108" t="n">
-        <v>0</v>
-      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
         <v>150.87</v>
       </c>
@@ -6960,49 +5260,33 @@
       <c r="F108" t="n">
         <v>0.7</v>
       </c>
-      <c r="G108" t="n">
-        <v>0</v>
-      </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>31.35</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="J108" t="n">
-        <v>31.35</v>
-      </c>
-      <c r="K108" t="n">
-        <v>2.52</v>
-      </c>
+        <v>1.15</v>
+      </c>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" t="n">
-        <v>1.15</v>
+        <v>424.22</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" t="n">
-        <v>424.22</v>
-      </c>
+        <v>343.12</v>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="O108" t="n">
-        <v>343.12</v>
-      </c>
-      <c r="P108" t="n">
-        <v>0</v>
-      </c>
+        <v>2.7</v>
+      </c>
+      <c r="P108" t="inlineStr"/>
       <c r="Q108" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R108" t="n">
-        <v>0</v>
-      </c>
+        <v>0.42</v>
+      </c>
+      <c r="R108" t="inlineStr"/>
       <c r="S108" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="T108" t="n">
-        <v>0</v>
-      </c>
-      <c r="U108" t="n">
         <v>230.51</v>
       </c>
     </row>
@@ -7012,9 +5296,7 @@
           <t>2023-12</t>
         </is>
       </c>
-      <c r="B109" t="n">
-        <v>0</v>
-      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
         <v>531.79</v>
       </c>
@@ -7027,49 +5309,35 @@
       <c r="F109" t="n">
         <v>0.5</v>
       </c>
-      <c r="G109" t="n">
-        <v>0</v>
-      </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>15.15</v>
       </c>
       <c r="J109" t="n">
-        <v>5.81</v>
+        <v>15.59</v>
       </c>
       <c r="K109" t="n">
-        <v>15.15</v>
+        <v>0.2</v>
       </c>
       <c r="L109" t="n">
-        <v>15.59</v>
+        <v>787.5699999999999</v>
       </c>
       <c r="M109" t="n">
-        <v>0.2</v>
+        <v>418.02</v>
       </c>
       <c r="N109" t="n">
-        <v>787.5699999999999</v>
+        <v>2</v>
       </c>
       <c r="O109" t="n">
-        <v>418.02</v>
-      </c>
-      <c r="P109" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q109" t="n">
         <v>2.31</v>
       </c>
-      <c r="R109" t="n">
-        <v>0</v>
-      </c>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
       <c r="S109" t="n">
-        <v>0</v>
-      </c>
-      <c r="T109" t="n">
-        <v>0</v>
-      </c>
-      <c r="U109" t="n">
         <v>339.01</v>
       </c>
     </row>
@@ -7079,9 +5347,7 @@
           <t>2024-01</t>
         </is>
       </c>
-      <c r="B110" t="n">
-        <v>0</v>
-      </c>
+      <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
         <v>119.5</v>
       </c>
@@ -7091,52 +5357,30 @@
       <c r="E110" t="n">
         <v>323.81</v>
       </c>
-      <c r="F110" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" t="n">
-        <v>0</v>
-      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>109.8</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="J110" t="n">
-        <v>109.8</v>
-      </c>
-      <c r="K110" t="n">
-        <v>2.4</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="K110" t="inlineStr"/>
       <c r="L110" t="n">
-        <v>0.9</v>
+        <v>369.4</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
-      </c>
-      <c r="N110" t="n">
-        <v>369.4</v>
-      </c>
-      <c r="O110" t="n">
         <v>168.4</v>
       </c>
-      <c r="P110" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
-      <c r="R110" t="n">
-        <v>0</v>
-      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
       <c r="S110" t="n">
-        <v>0</v>
-      </c>
-      <c r="T110" t="n">
-        <v>0</v>
-      </c>
-      <c r="U110" t="n">
         <v>67.86</v>
       </c>
     </row>
@@ -7146,9 +5390,7 @@
           <t>2024-02</t>
         </is>
       </c>
-      <c r="B111" t="n">
-        <v>0</v>
-      </c>
+      <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
         <v>72.59999999999999</v>
       </c>
@@ -7158,52 +5400,32 @@
       <c r="E111" t="n">
         <v>423.76</v>
       </c>
-      <c r="F111" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" t="n">
-        <v>0</v>
-      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>32.3</v>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="K111" t="n">
         <v>8.699999999999999</v>
       </c>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>328.32</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
-      </c>
-      <c r="N111" t="n">
-        <v>328.32</v>
-      </c>
+        <v>304.5</v>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="O111" t="n">
-        <v>304.5</v>
-      </c>
-      <c r="P111" t="n">
-        <v>0</v>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="P111" t="inlineStr"/>
       <c r="Q111" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="R111" t="n">
-        <v>0</v>
-      </c>
+        <v>0.42</v>
+      </c>
+      <c r="R111" t="inlineStr"/>
       <c r="S111" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="T111" t="n">
-        <v>0</v>
-      </c>
-      <c r="U111" t="n">
         <v>55.34</v>
       </c>
     </row>
@@ -7213,9 +5435,7 @@
           <t>2024-03</t>
         </is>
       </c>
-      <c r="B112" t="n">
-        <v>0</v>
-      </c>
+      <c r="B112" t="inlineStr"/>
       <c r="C112" t="n">
         <v>391</v>
       </c>
@@ -7225,52 +5445,32 @@
       <c r="E112" t="n">
         <v>441.9</v>
       </c>
-      <c r="F112" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" t="n">
-        <v>0</v>
-      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="J112" t="n">
-        <v>59</v>
-      </c>
-      <c r="K112" t="n">
-        <v>9.5</v>
-      </c>
+        <v>10.6</v>
+      </c>
+      <c r="K112" t="inlineStr"/>
       <c r="L112" t="n">
-        <v>10.6</v>
+        <v>354.71</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
-      </c>
-      <c r="N112" t="n">
-        <v>354.71</v>
-      </c>
+        <v>45.2</v>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="O112" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="P112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q112" t="n">
         <v>12.8</v>
       </c>
-      <c r="R112" t="n">
-        <v>0</v>
-      </c>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
       <c r="S112" t="n">
-        <v>0</v>
-      </c>
-      <c r="T112" t="n">
-        <v>0</v>
-      </c>
-      <c r="U112" t="n">
         <v>88.59999999999999</v>
       </c>
     </row>
@@ -7280,9 +5480,7 @@
           <t>2024-04</t>
         </is>
       </c>
-      <c r="B113" t="n">
-        <v>0</v>
-      </c>
+      <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
         <v>126.1</v>
       </c>
@@ -7295,49 +5493,29 @@
       <c r="F113" t="n">
         <v>0.8</v>
       </c>
-      <c r="G113" t="n">
-        <v>0</v>
-      </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>17.1</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="J113" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="K113" t="n">
-        <v>1.6</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
-      </c>
-      <c r="N113" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O113" t="n">
         <v>333.5</v>
       </c>
-      <c r="P113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
-      <c r="R113" t="n">
-        <v>0</v>
-      </c>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
       <c r="S113" t="n">
-        <v>0</v>
-      </c>
-      <c r="T113" t="n">
-        <v>0</v>
-      </c>
-      <c r="U113" t="n">
         <v>104.94</v>
       </c>
     </row>
@@ -7347,9 +5525,7 @@
           <t>2024-05</t>
         </is>
       </c>
-      <c r="B114" t="n">
-        <v>0</v>
-      </c>
+      <c r="B114" t="inlineStr"/>
       <c r="C114" t="n">
         <v>229.1</v>
       </c>
@@ -7359,52 +5535,30 @@
       <c r="E114" t="n">
         <v>487.6900000000001</v>
       </c>
-      <c r="F114" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" t="n">
-        <v>0</v>
-      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>14.4</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J114" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K114" t="n">
-        <v>9.300000000000001</v>
-      </c>
+        <v>6.2</v>
+      </c>
+      <c r="K114" t="inlineStr"/>
       <c r="L114" t="n">
-        <v>6.2</v>
+        <v>0.89</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
-      </c>
-      <c r="N114" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="O114" t="n">
         <v>145.3</v>
       </c>
-      <c r="P114" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
-      <c r="R114" t="n">
-        <v>0</v>
-      </c>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
       <c r="S114" t="n">
-        <v>0</v>
-      </c>
-      <c r="T114" t="n">
-        <v>0</v>
-      </c>
-      <c r="U114" t="n">
         <v>96.62</v>
       </c>
     </row>
@@ -7414,9 +5568,7 @@
           <t>2024-06</t>
         </is>
       </c>
-      <c r="B115" t="n">
-        <v>0</v>
-      </c>
+      <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
         <v>12.2</v>
       </c>
@@ -7426,52 +5578,34 @@
       <c r="E115" t="n">
         <v>446.9</v>
       </c>
-      <c r="F115" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" t="n">
-        <v>0</v>
-      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>23.74</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="J115" t="n">
-        <v>23.74</v>
-      </c>
-      <c r="K115" t="n">
-        <v>58</v>
-      </c>
+        <v>7.7</v>
+      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="n">
-        <v>7.7</v>
+        <v>2.32</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>316</v>
       </c>
       <c r="N115" t="n">
-        <v>2.32</v>
+        <v>1.68</v>
       </c>
       <c r="O115" t="n">
-        <v>316</v>
-      </c>
-      <c r="P115" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q115" t="n">
         <v>37.8</v>
       </c>
-      <c r="R115" t="n">
-        <v>0</v>
-      </c>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
       <c r="S115" t="n">
-        <v>0</v>
-      </c>
-      <c r="T115" t="n">
-        <v>0</v>
-      </c>
-      <c r="U115" t="n">
         <v>103.21</v>
       </c>
     </row>
@@ -7481,9 +5615,7 @@
           <t>2024-07</t>
         </is>
       </c>
-      <c r="B116" t="n">
-        <v>0</v>
-      </c>
+      <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
         <v>24.1</v>
       </c>
@@ -7496,49 +5628,27 @@
       <c r="F116" t="n">
         <v>0.5</v>
       </c>
-      <c r="G116" t="n">
-        <v>0</v>
-      </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K116" t="n">
         <v>0.6</v>
       </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
-      </c>
-      <c r="N116" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O116" t="n">
         <v>165.2</v>
       </c>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
-      <c r="R116" t="n">
-        <v>0</v>
-      </c>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
       <c r="S116" t="n">
-        <v>0</v>
-      </c>
-      <c r="T116" t="n">
-        <v>0</v>
-      </c>
-      <c r="U116" t="n">
         <v>38.88</v>
       </c>
     </row>
@@ -7548,9 +5658,7 @@
           <t>2024-08</t>
         </is>
       </c>
-      <c r="B117" t="n">
-        <v>0</v>
-      </c>
+      <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
         <v>5.7</v>
       </c>
@@ -7560,52 +5668,32 @@
       <c r="E117" t="n">
         <v>133.5</v>
       </c>
-      <c r="F117" t="n">
-        <v>0</v>
-      </c>
-      <c r="G117" t="n">
-        <v>0</v>
-      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="K117" t="n">
         <v>6.4</v>
       </c>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
-      </c>
-      <c r="N117" t="n">
-        <v>3.82</v>
-      </c>
+        <v>409.3</v>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="O117" t="n">
-        <v>409.3</v>
-      </c>
-      <c r="P117" t="n">
-        <v>0</v>
-      </c>
+        <v>4.300000000000001</v>
+      </c>
+      <c r="P117" t="inlineStr"/>
       <c r="Q117" t="n">
-        <v>4.300000000000001</v>
-      </c>
-      <c r="R117" t="n">
-        <v>0</v>
-      </c>
+        <v>0.4</v>
+      </c>
+      <c r="R117" t="inlineStr"/>
       <c r="S117" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="T117" t="n">
-        <v>0</v>
-      </c>
-      <c r="U117" t="n">
         <v>142.22</v>
       </c>
     </row>
@@ -7615,9 +5703,7 @@
           <t>2024-09</t>
         </is>
       </c>
-      <c r="B118" t="n">
-        <v>0</v>
-      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="n">
         <v>49.87</v>
       </c>
@@ -7627,52 +5713,32 @@
       <c r="E118" t="n">
         <v>730.3399999999999</v>
       </c>
-      <c r="F118" t="n">
-        <v>0</v>
-      </c>
-      <c r="G118" t="n">
-        <v>0</v>
-      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>98.5</v>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>31.5</v>
       </c>
       <c r="J118" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="K118" t="n">
-        <v>31.5</v>
-      </c>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" t="n">
-        <v>9.199999999999999</v>
+        <v>5.31</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
-      </c>
-      <c r="N118" t="n">
-        <v>5.31</v>
-      </c>
+        <v>901.5999999999999</v>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="O118" t="n">
-        <v>901.5999999999999</v>
-      </c>
-      <c r="P118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q118" t="n">
         <v>1.2</v>
       </c>
-      <c r="R118" t="n">
-        <v>0</v>
-      </c>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
       <c r="S118" t="n">
-        <v>0</v>
-      </c>
-      <c r="T118" t="n">
-        <v>0</v>
-      </c>
-      <c r="U118" t="n">
         <v>138.52</v>
       </c>
     </row>
@@ -7682,9 +5748,7 @@
           <t>2024-10</t>
         </is>
       </c>
-      <c r="B119" t="n">
-        <v>0</v>
-      </c>
+      <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
         <v>63</v>
       </c>
@@ -7697,49 +5761,29 @@
       <c r="F119" t="n">
         <v>0.4</v>
       </c>
-      <c r="G119" t="n">
-        <v>0</v>
-      </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>25.9</v>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="K119" t="n">
         <v>13.3</v>
       </c>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>41.09999999999999</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>279.4</v>
       </c>
       <c r="N119" t="n">
-        <v>41.09999999999999</v>
-      </c>
-      <c r="O119" t="n">
-        <v>279.4</v>
-      </c>
-      <c r="P119" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
-      <c r="R119" t="n">
-        <v>0</v>
-      </c>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr"/>
       <c r="S119" t="n">
-        <v>0</v>
-      </c>
-      <c r="T119" t="n">
-        <v>0</v>
-      </c>
-      <c r="U119" t="n">
         <v>135.1</v>
       </c>
     </row>
@@ -7749,9 +5793,7 @@
           <t>2024-11</t>
         </is>
       </c>
-      <c r="B120" t="n">
-        <v>0</v>
-      </c>
+      <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
         <v>154.3</v>
       </c>
@@ -7761,52 +5803,32 @@
       <c r="E120" t="n">
         <v>537.6</v>
       </c>
-      <c r="F120" t="n">
-        <v>0</v>
-      </c>
-      <c r="G120" t="n">
-        <v>0</v>
-      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>33.59999999999999</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" t="n">
-        <v>33.59999999999999</v>
-      </c>
-      <c r="K120" t="n">
         <v>2.6</v>
       </c>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>440.84</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>326.2</v>
       </c>
       <c r="N120" t="n">
-        <v>440.84</v>
+        <v>1.4</v>
       </c>
       <c r="O120" t="n">
-        <v>326.2</v>
-      </c>
-      <c r="P120" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q120" t="n">
         <v>2.7</v>
       </c>
-      <c r="R120" t="n">
-        <v>0</v>
-      </c>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr"/>
       <c r="S120" t="n">
-        <v>0</v>
-      </c>
-      <c r="T120" t="n">
-        <v>0</v>
-      </c>
-      <c r="U120" t="n">
         <v>262.18</v>
       </c>
     </row>
@@ -7816,9 +5838,7 @@
           <t>2024-12</t>
         </is>
       </c>
-      <c r="B121" t="n">
-        <v>0</v>
-      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
         <v>538.4</v>
       </c>
@@ -7828,52 +5848,34 @@
       <c r="E121" t="n">
         <v>930.28</v>
       </c>
-      <c r="F121" t="n">
-        <v>0</v>
-      </c>
-      <c r="G121" t="n">
-        <v>0</v>
-      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" t="n">
-        <v>5.8</v>
-      </c>
+        <v>18.4</v>
+      </c>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" t="n">
-        <v>18.4</v>
+        <v>1.2</v>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1740.77</v>
       </c>
       <c r="M121" t="n">
-        <v>1.2</v>
+        <v>921.4</v>
       </c>
       <c r="N121" t="n">
-        <v>1740.77</v>
+        <v>17.1</v>
       </c>
       <c r="O121" t="n">
-        <v>921.4000000000001</v>
-      </c>
-      <c r="P121" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="Q121" t="n">
         <v>1.9</v>
       </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr"/>
       <c r="S121" t="n">
-        <v>0</v>
-      </c>
-      <c r="T121" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" t="n">
         <v>764.4399999999999</v>
       </c>
     </row>
@@ -7883,9 +5885,7 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="B122" t="n">
-        <v>0</v>
-      </c>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" t="n">
         <v>129.3</v>
       </c>
@@ -7895,52 +5895,32 @@
       <c r="E122" t="n">
         <v>322.1</v>
       </c>
-      <c r="F122" t="n">
-        <v>0</v>
-      </c>
-      <c r="G122" t="n">
-        <v>0</v>
-      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>109.8</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J122" t="n">
-        <v>109.8</v>
-      </c>
-      <c r="K122" t="n">
-        <v>2.5</v>
-      </c>
+        <v>0.4</v>
+      </c>
+      <c r="K122" t="inlineStr"/>
       <c r="L122" t="n">
-        <v>0.4</v>
+        <v>450.07</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="N122" t="n">
-        <v>450.07</v>
-      </c>
-      <c r="O122" t="n">
-        <v>164</v>
-      </c>
-      <c r="P122" t="n">
         <v>5.25</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0</v>
-      </c>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr"/>
       <c r="S122" t="n">
-        <v>0</v>
-      </c>
-      <c r="T122" t="n">
-        <v>0</v>
-      </c>
-      <c r="U122" t="n">
         <v>69.2</v>
       </c>
     </row>
@@ -7950,9 +5930,7 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="B123" t="n">
-        <v>0</v>
-      </c>
+      <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
         <v>77.59999999999999</v>
       </c>
@@ -7965,49 +5943,31 @@
       <c r="F123" t="n">
         <v>0.7</v>
       </c>
-      <c r="G123" t="n">
-        <v>0</v>
-      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>36.4</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="K123" t="n">
         <v>8.699999999999999</v>
       </c>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>376.72</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>580.5</v>
       </c>
       <c r="N123" t="n">
-        <v>376.72</v>
+        <v>1.4</v>
       </c>
       <c r="O123" t="n">
-        <v>580.5</v>
-      </c>
-      <c r="P123" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q123" t="n">
         <v>0.4</v>
       </c>
-      <c r="R123" t="n">
-        <v>0</v>
-      </c>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr"/>
       <c r="S123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U123" t="n">
         <v>60.13</v>
       </c>
     </row>
@@ -8017,9 +5977,7 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="B124" t="n">
-        <v>0</v>
-      </c>
+      <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
         <v>411.5</v>
       </c>
@@ -8029,52 +5987,32 @@
       <c r="E124" t="n">
         <v>447.4</v>
       </c>
-      <c r="F124" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" t="n">
-        <v>0</v>
-      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>60.4</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J124" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="K124" t="n">
-        <v>9.699999999999999</v>
-      </c>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K124" t="inlineStr"/>
       <c r="L124" t="n">
-        <v>9.800000000000001</v>
+        <v>335.32</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
-      </c>
-      <c r="N124" t="n">
-        <v>335.32</v>
-      </c>
+        <v>109.58</v>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="O124" t="n">
-        <v>109.58</v>
-      </c>
-      <c r="P124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q124" t="n">
         <v>1.1</v>
       </c>
-      <c r="R124" t="n">
-        <v>0</v>
-      </c>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
       <c r="S124" t="n">
-        <v>0</v>
-      </c>
-      <c r="T124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U124" t="n">
         <v>93.09999999999999</v>
       </c>
     </row>
@@ -8084,9 +6022,7 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="B125" t="n">
-        <v>0</v>
-      </c>
+      <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
         <v>128.1</v>
       </c>
@@ -8099,49 +6035,31 @@
       <c r="F125" t="n">
         <v>2.9</v>
       </c>
-      <c r="G125" t="n">
-        <v>0</v>
-      </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="J125" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="K125" t="n">
-        <v>1.7</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K125" t="inlineStr"/>
       <c r="L125" t="n">
-        <v>2</v>
+        <v>72.2</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="N125" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="O125" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="P125" t="n">
         <v>0.35</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0</v>
-      </c>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr"/>
       <c r="S125" t="n">
-        <v>0</v>
-      </c>
-      <c r="T125" t="n">
-        <v>0</v>
-      </c>
-      <c r="U125" t="n">
         <v>85.80000000000001</v>
       </c>
     </row>
@@ -8151,9 +6069,7 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="B126" t="n">
-        <v>0</v>
-      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
         <v>235.7</v>
       </c>
@@ -8166,49 +6082,29 @@
       <c r="F126" t="n">
         <v>0.9</v>
       </c>
-      <c r="G126" t="n">
-        <v>0</v>
-      </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>15.6</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J126" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="K126" t="n">
-        <v>9.6</v>
-      </c>
+        <v>6.3</v>
+      </c>
+      <c r="K126" t="inlineStr"/>
       <c r="L126" t="n">
-        <v>6.3</v>
+        <v>1.51</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
-      </c>
-      <c r="N126" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="O126" t="n">
         <v>174.45</v>
       </c>
-      <c r="P126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0</v>
-      </c>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
       <c r="S126" t="n">
-        <v>0</v>
-      </c>
-      <c r="T126" t="n">
-        <v>0</v>
-      </c>
-      <c r="U126" t="n">
         <v>96.61000000000001</v>
       </c>
     </row>
@@ -8218,64 +6114,44 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="B127" t="n">
-        <v>0</v>
-      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="n">
         <v>12.2</v>
       </c>
       <c r="D127" t="n">
-        <v>41.59999999999999</v>
+        <v>41.6</v>
       </c>
       <c r="E127" t="n">
         <v>688</v>
       </c>
-      <c r="F127" t="n">
-        <v>0</v>
-      </c>
-      <c r="G127" t="n">
-        <v>0</v>
-      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>19.7</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>59.92</v>
       </c>
       <c r="J127" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="K127" t="n">
-        <v>59.92</v>
-      </c>
+        <v>6.4</v>
+      </c>
+      <c r="K127" t="inlineStr"/>
       <c r="L127" t="n">
-        <v>6.4</v>
+        <v>56.94</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>317.85</v>
       </c>
       <c r="N127" t="n">
-        <v>56.94</v>
+        <v>3.98</v>
       </c>
       <c r="O127" t="n">
-        <v>317.85</v>
-      </c>
-      <c r="P127" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="Q127" t="n">
         <v>28.3</v>
       </c>
-      <c r="R127" t="n">
-        <v>0</v>
-      </c>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
       <c r="S127" t="n">
-        <v>0</v>
-      </c>
-      <c r="T127" t="n">
-        <v>0</v>
-      </c>
-      <c r="U127" t="n">
         <v>105</v>
       </c>
     </row>
@@ -8285,9 +6161,7 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="B128" t="n">
-        <v>0</v>
-      </c>
+      <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
         <v>25.17</v>
       </c>
@@ -8300,50 +6174,28 @@
       <c r="F128" t="n">
         <v>0.6</v>
       </c>
-      <c r="G128" t="n">
-        <v>0</v>
-      </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="K128" t="n">
         <v>0.6</v>
       </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>13.58</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
-      </c>
-      <c r="N128" t="n">
-        <v>13.58</v>
-      </c>
-      <c r="O128" t="n">
         <v>163.8</v>
       </c>
-      <c r="P128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
-      <c r="R128" t="n">
-        <v>0</v>
-      </c>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr"/>
       <c r="S128" t="n">
-        <v>0</v>
-      </c>
-      <c r="T128" t="n">
-        <v>0</v>
-      </c>
-      <c r="U128" t="n">
-        <v>44.09999999999999</v>
+        <v>44.1</v>
       </c>
     </row>
   </sheetData>
